--- a/BNTable.xlsx
+++ b/BNTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangqiqian/Desktop/ST-RTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14634155-5604-7B44-B7FF-53BCBAD8E543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BABA5F-60B0-DC4D-ACA9-A3B220CC3AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26540" activeTab="4" xr2:uid="{37465112-FFA5-A943-9908-D2C76DED5922}"/>
+    <workbookView xWindow="11680" yWindow="29540" windowWidth="30240" windowHeight="18900" firstSheet="2" activeTab="5" xr2:uid="{37465112-FFA5-A943-9908-D2C76DED5922}"/>
   </bookViews>
   <sheets>
     <sheet name="肇因研判依賴於號誌種類" sheetId="4" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="快車道、一般車道依賴於肇因研判" sheetId="3" r:id="rId3"/>
     <sheet name="道路型態依賴於肇因研判、號誌種類" sheetId="1" r:id="rId4"/>
     <sheet name="肇因依賴於號誌和道路型態(有blacklist)" sheetId="5" r:id="rId5"/>
+    <sheet name="肇因依賴於速限和道路類別_市區道路" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="98">
   <si>
     <t>號誌種類</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -330,6 +331,27 @@
   </si>
   <si>
     <t>坡路</t>
+  </si>
+  <si>
+    <t>迴轉未依規定</t>
+  </si>
+  <si>
+    <t>30-39</t>
+  </si>
+  <si>
+    <t>0-9</t>
+  </si>
+  <si>
+    <t>40-49</t>
+  </si>
+  <si>
+    <t>速限</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>相關跡證不足且無具體影像紀錄，
+當事人各執一詞，經分析後無法釐清肇事原因</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -390,7 +412,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -443,6 +465,17 @@
         <color auto="1"/>
       </right>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -457,7 +490,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -482,6 +515,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -494,10 +530,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2952,7 +3021,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="6"/>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>34</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -2967,7 +3036,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="6"/>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="12" t="s">
         <v>66</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -2982,7 +3051,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="6"/>
-      <c r="B5" s="12"/>
+      <c r="B5" s="13"/>
       <c r="C5" s="2" t="s">
         <v>82</v>
       </c>
@@ -2995,7 +3064,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="6"/>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -3010,7 +3079,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="6"/>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>90</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -3057,7 +3126,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="6"/>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="14" t="s">
         <v>66</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -3072,7 +3141,7 @@
     </row>
     <row r="11" spans="1:5" ht="32" customHeight="1">
       <c r="A11" s="6"/>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -3117,7 +3186,7 @@
     </row>
     <row r="14" spans="1:5" ht="32" customHeight="1">
       <c r="A14" s="6"/>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>87</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -3192,7 +3261,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="7"/>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="12" t="s">
         <v>89</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -3207,7 +3276,7 @@
     </row>
     <row r="20" spans="1:5" ht="16" customHeight="1">
       <c r="A20" s="7"/>
-      <c r="B20" s="12"/>
+      <c r="B20" s="13"/>
       <c r="C20" s="2" t="s">
         <v>83</v>
       </c>
@@ -3280,7 +3349,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="7"/>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="12" t="s">
         <v>86</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -3295,7 +3364,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="7"/>
-      <c r="B26" s="12"/>
+      <c r="B26" s="13"/>
       <c r="C26" s="2" t="s">
         <v>81</v>
       </c>
@@ -3308,7 +3377,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="7"/>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="14" t="s">
         <v>36</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -3364,16 +3433,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="7"/>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="10">
         <v>0.1744</v>
       </c>
-      <c r="E31" s="10">
+      <c r="E31" s="11">
         <v>1487</v>
       </c>
     </row>
@@ -3427,4 +3496,984 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59CC7DFE-23E2-7E47-8BF1-807528FEF86A}">
+  <dimension ref="A1:F59"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" style="16" customWidth="1"/>
+    <col min="3" max="3" width="13" style="8" customWidth="1"/>
+    <col min="4" max="4" width="41.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="21">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.12479999999999999</v>
+      </c>
+      <c r="F2" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="19"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.1862</v>
+      </c>
+      <c r="F3" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="32">
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3.7199999999999997E-2</v>
+      </c>
+      <c r="F4" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="2">
+        <v>4.0800000000000003E-2</v>
+      </c>
+      <c r="F5" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5.9400000000000001E-2</v>
+      </c>
+      <c r="F6" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="2">
+        <v>6.2899999999999998E-2</v>
+      </c>
+      <c r="F7" s="2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="2">
+        <v>6.3700000000000007E-2</v>
+      </c>
+      <c r="F8" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="2">
+        <v>6.4399999999999999E-2</v>
+      </c>
+      <c r="F9" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="2">
+        <v>7.9399999999999998E-2</v>
+      </c>
+      <c r="F10" s="2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="2">
+        <v>8.1500000000000003E-2</v>
+      </c>
+      <c r="F11" s="2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.1116</v>
+      </c>
+      <c r="F12" s="2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0.18379999999999999</v>
+      </c>
+      <c r="F13" s="2">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0.27150000000000002</v>
+      </c>
+      <c r="F14" s="2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0.2049</v>
+      </c>
+      <c r="F15" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="2">
+        <v>6.9500000000000006E-2</v>
+      </c>
+      <c r="F16" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0.114</v>
+      </c>
+      <c r="F17" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0.21</v>
+      </c>
+      <c r="F18" s="2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0.4355</v>
+      </c>
+      <c r="F19" s="2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0.15049999999999999</v>
+      </c>
+      <c r="F20" s="2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="19"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0.15809999999999999</v>
+      </c>
+      <c r="F21" s="2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="19"/>
+      <c r="B22" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" s="2">
+        <v>4.6600000000000003E-2</v>
+      </c>
+      <c r="F22" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" s="2">
+        <v>6.4600000000000005E-2</v>
+      </c>
+      <c r="F23" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" s="2">
+        <v>8.2699999999999996E-2</v>
+      </c>
+      <c r="F24" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15" customHeight="1">
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="2">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="F25" s="2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0.1605</v>
+      </c>
+      <c r="F26" s="2">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0.20569999999999999</v>
+      </c>
+      <c r="F27" s="2">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28" s="2">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="F28" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15" customHeight="1">
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E29" s="2">
+        <v>3.3500000000000002E-2</v>
+      </c>
+      <c r="F29" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E30" s="2">
+        <v>3.3500000000000002E-2</v>
+      </c>
+      <c r="F30" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E31" s="2">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="F31" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="2">
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="F32" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="19"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0.1351</v>
+      </c>
+      <c r="F33" s="2">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="19"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0.14360000000000001</v>
+      </c>
+      <c r="F34" s="2">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="19"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0.3972</v>
+      </c>
+      <c r="F35" s="2">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="19"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E36" s="2">
+        <v>5.2900000000000003E-2</v>
+      </c>
+      <c r="F36" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="19"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E37" s="2">
+        <v>5.6599999999999998E-2</v>
+      </c>
+      <c r="F37" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="19"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E38" s="2">
+        <v>7.4700000000000003E-2</v>
+      </c>
+      <c r="F38" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="19"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E39" s="2">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="F39" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="19"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E40" s="2">
+        <v>9.4299999999999995E-2</v>
+      </c>
+      <c r="F40" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="19"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0.10150000000000001</v>
+      </c>
+      <c r="F41" s="2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="19"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E42" s="2">
+        <v>0.12330000000000001</v>
+      </c>
+      <c r="F42" s="2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="19"/>
+      <c r="B43" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C43" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E43" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F43" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="19"/>
+      <c r="B44" s="19"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E44" s="2">
+        <v>7.51E-2</v>
+      </c>
+      <c r="F44" s="2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="19"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="25"/>
+      <c r="D45" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E45" s="2">
+        <v>9.6699999999999994E-2</v>
+      </c>
+      <c r="F45" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="19"/>
+      <c r="B46" s="19"/>
+      <c r="C46" s="25"/>
+      <c r="D46" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E46" s="2">
+        <v>0.1069</v>
+      </c>
+      <c r="F46" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="19"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="24"/>
+      <c r="D47" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E47" s="2">
+        <v>0.13739999999999999</v>
+      </c>
+      <c r="F47" s="2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="19"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E48" s="2">
+        <v>0.16750000000000001</v>
+      </c>
+      <c r="F48" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="19"/>
+      <c r="B49" s="19"/>
+      <c r="C49" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E49" s="2">
+        <v>2.3199999999999998E-2</v>
+      </c>
+      <c r="F49" s="2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="19"/>
+      <c r="B50" s="19"/>
+      <c r="C50" s="25"/>
+      <c r="D50" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E50" s="2">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="F50" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="32">
+      <c r="A51" s="19"/>
+      <c r="B51" s="19"/>
+      <c r="C51" s="25"/>
+      <c r="D51" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E51" s="2">
+        <v>2.8500000000000001E-2</v>
+      </c>
+      <c r="F51" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="19"/>
+      <c r="B52" s="19"/>
+      <c r="C52" s="25"/>
+      <c r="D52" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E52" s="2">
+        <v>3.7600000000000001E-2</v>
+      </c>
+      <c r="F52" s="2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="19"/>
+      <c r="B53" s="19"/>
+      <c r="C53" s="25"/>
+      <c r="D53" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E53" s="2">
+        <v>4.3299999999999998E-2</v>
+      </c>
+      <c r="F53" s="2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="19"/>
+      <c r="B54" s="19"/>
+      <c r="C54" s="25"/>
+      <c r="D54" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E54" s="2">
+        <v>6.9599999999999995E-2</v>
+      </c>
+      <c r="F54" s="2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="19"/>
+      <c r="B55" s="19"/>
+      <c r="C55" s="25"/>
+      <c r="D55" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E55" s="2">
+        <v>7.7700000000000005E-2</v>
+      </c>
+      <c r="F55" s="2">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="19"/>
+      <c r="B56" s="19"/>
+      <c r="C56" s="25"/>
+      <c r="D56" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E56" s="2">
+        <v>7.8799999999999995E-2</v>
+      </c>
+      <c r="F56" s="2">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="19"/>
+      <c r="B57" s="19"/>
+      <c r="C57" s="25"/>
+      <c r="D57" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E57" s="2">
+        <v>8.6499999999999994E-2</v>
+      </c>
+      <c r="F57" s="2">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="19"/>
+      <c r="B58" s="19"/>
+      <c r="C58" s="25"/>
+      <c r="D58" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E58" s="2">
+        <v>0.1361</v>
+      </c>
+      <c r="F58" s="2">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="20"/>
+      <c r="B59" s="20"/>
+      <c r="C59" s="24"/>
+      <c r="D59" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E59" s="2">
+        <v>0.16919999999999999</v>
+      </c>
+      <c r="F59" s="2">
+        <v>481</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F59">
+    <sortCondition ref="A2:A59"/>
+    <sortCondition ref="B2:B59"/>
+    <sortCondition ref="C2:C59"/>
+    <sortCondition ref="E2:E59"/>
+    <sortCondition ref="F2:F59"/>
+  </sortState>
+  <mergeCells count="17">
+    <mergeCell ref="C43:C47"/>
+    <mergeCell ref="C49:C59"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B22:B42"/>
+    <mergeCell ref="B43:B59"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C13"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="C28:C35"/>
+    <mergeCell ref="C36:C42"/>
+    <mergeCell ref="A2:A14"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="A20:A59"/>
+    <mergeCell ref="B2:B14"/>
+    <mergeCell ref="B15:B18"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="E27:E31 E2:E25">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F27:F31 F2:F25">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="3" tint="0.89999084444715716"/>
+        <color theme="3" tint="0.499984740745262"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="3" tint="0.89999084444715716"/>
+        <color theme="7" tint="0.39997558519241921"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:C2 C16">
+    <cfRule type="dataBar" priority="23">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{E3C5D9D4-626D-D446-BFB3-E606305F35DF}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{E3C5D9D4-626D-D446-BFB3-E606305F35DF}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>B2:C2 C16</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
 </file>
--- a/BNTable.xlsx
+++ b/BNTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangqiqian/Desktop/ST-RTA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BABA5F-60B0-DC4D-ACA9-A3B220CC3AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98FD85D9-C6C3-2A42-9B53-9D3A7D542B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11680" yWindow="29540" windowWidth="30240" windowHeight="18900" firstSheet="2" activeTab="5" xr2:uid="{37465112-FFA5-A943-9908-D2C76DED5922}"/>
   </bookViews>
@@ -4388,13 +4388,6 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F59">
-    <sortCondition ref="A2:A59"/>
-    <sortCondition ref="B2:B59"/>
-    <sortCondition ref="C2:C59"/>
-    <sortCondition ref="E2:E59"/>
-    <sortCondition ref="F2:F59"/>
-  </sortState>
   <mergeCells count="17">
     <mergeCell ref="C43:C47"/>
     <mergeCell ref="C49:C59"/>
@@ -4416,7 +4409,7 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="E27:E31 E2:E25">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4426,7 +4419,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F27:F31 F2:F25">
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4434,7 +4427,7 @@
         <color theme="3" tint="0.499984740745262"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4444,7 +4437,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:C2 C16">
-    <cfRule type="dataBar" priority="23">
+    <cfRule type="dataBar" priority="26">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4455,6 +4448,34 @@
           <x14:id>{E3C5D9D4-626D-D446-BFB3-E606305F35DF}</x14:id>
         </ext>
       </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E59">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="5" tint="0.79998168889431442"/>
+        <color theme="5" tint="-0.249977111117893"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="5" tint="0.79998168889431442"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F59">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="3" tint="0.89999084444715716"/>
+        <color rgb="FF00B0F0"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
